--- a/database.xlsx
+++ b/database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,36 @@
         <is>
           <t>Limit</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>renzo rocha</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>123456</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>eric renzo rocha</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Full-Time</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,36 +508,6 @@
         <is>
           <t>Limit</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>renzo rocha</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>123456</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>eric renzo rocha</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Full-Time</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
